--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566660225</v>
+        <v>46157.93093574997</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93093574997</v>
+        <v>46157.93170309559</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93170309559</v>
+        <v>46157.93398500351</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398500351</v>
+        <v>46157.93716231535</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716231535</v>
+        <v>46158.28214836158</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214836158</v>
+        <v>46158.29676313354</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676313354</v>
+        <v>46158.29812948007</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29812948007</v>
+        <v>46158.33385828784</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33385828784</v>
+        <v>46158.36855589048</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/9. ООО Бит Мастер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855589048</v>
+        <v>46158.37286314043</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
